--- a/Sample_run/1/student/duynthe180374/TC1/GradeDetail.xlsx
+++ b/Sample_run/1/student/duynthe180374/TC1/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>39904</x:v>
+        <x:v>42934</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1097,7 +1097,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>39904</x:v>
+        <x:v>42934</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>39904</x:v>
+        <x:v>42934</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1206,7 +1206,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>39904</x:v>
+        <x:v>42934</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1265,7 +1265,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>39904</x:v>
+        <x:v>42934</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>52</x:v>
@@ -1321,7 +1321,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>39904</x:v>
+        <x:v>42934</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>52</x:v>
@@ -1374,7 +1374,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>39904</x:v>
+        <x:v>42934</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1430,7 +1430,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>39904</x:v>
+        <x:v>42934</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>4000</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>39904</x:v>
+        <x:v>42934</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>
